--- a/enrollment/025_temporary_employee_payroll_form--enrollment.xlsx
+++ b/enrollment/025_temporary_employee_payroll_form--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'de'}</t>
+          <t>de</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'DE'}</t>
+          <t>DE</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'ga'}</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'GA'}</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'me'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'ME'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'mi'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'MI'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'mo'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'MO'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'MS'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'mt'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'MT'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'nc'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'NC'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'ne'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'NE'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'nv'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'NV'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'oh'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'OH'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'ok'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'OK'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'or'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'OR'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'sc'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'SC'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'sd'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'SD'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'tn'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'TN'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'ut'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'UT'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'va'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'VA'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'vt'}</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'VT'}</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'wv'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'WV'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'wi'}</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'WI'}</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'wy'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'WY'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'ein'}</t>
+          <t>ein</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'EIN'}</t>
+          <t>EIN</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'ssn'}</t>
+          <t>ssn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'SSN'}</t>
+          <t>SSN</t>
         </is>
       </c>
     </row>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'itin'}</t>
+          <t>itin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'ITIN'}</t>
+          <t>ITIN</t>
         </is>
       </c>
     </row>
